--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484238_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484238_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0716</v>
+        <v>3.0933</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7168</v>
+        <v>3.5751</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6451</v>
+        <v>-0.4817</v>
       </c>
       <c r="G2" t="n">
         <v>0.1483</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1503</v>
+        <v>0.172</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1432</v>
+        <v>0.0015</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0071</v>
+        <v>0.1705</v>
       </c>
       <c r="V2" t="n">
         <v>2.3824</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1202</v>
+        <v>2.8303</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4925</v>
+        <v>2.9575</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3722</v>
+        <v>-0.1271</v>
       </c>
       <c r="G3" t="n">
         <v>0.4472</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5809</v>
+        <v>-0.8708</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6987</v>
+        <v>-0.2337</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8822</v>
+        <v>-0.6371</v>
       </c>
       <c r="V3" t="n">
         <v>1.4959</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6683</v>
+        <v>1.8027</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0772</v>
+        <v>2.2389</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4089</v>
+        <v>-0.4361</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5089</v>
@@ -766,13 +766,13 @@
         <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7995</v>
+        <v>-0.6651</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.6857</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0478</v>
+        <v>0.0206</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8762</v>
+        <v>-1.0179</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.662</v>
+        <v>-0.8037</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2142</v>
@@ -844,10 +844,10 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5998</v>
+        <v>0.4581</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2642</v>
+        <v>0.1225</v>
       </c>
       <c r="U5" t="n">
         <v>0.3356</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.26</v>
+        <v>-1.7411</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2315</v>
+        <v>1.6155</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4915</v>
+        <v>-3.3566</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9957</v>
+        <v>0.4251</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3615</v>
+        <v>1.2484</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6342</v>
+        <v>-0.8233</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3909</v>
+        <v>2.6822</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3505</v>
+        <v>2.5608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0.1214</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3866</v>
+        <v>-2.2571</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.712</v>
+        <v>-1.3123</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6747</v>
+        <v>-0.9447</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4269</v>
+        <v>-1.1782</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8173</v>
+        <v>-0.6444</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6096</v>
+        <v>-0.5339</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8865</v>
+        <v>-2.16</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8251</v>
+        <v>-1.7449</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8584</v>
+        <v>-1.7431</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6835</v>
+        <v>-0.0018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4251</v>
+        <v>-0.4214</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2484</v>
+        <v>-1.0834</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8233</v>
+        <v>0.6621</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6822</v>
+        <v>1.0171</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5608</v>
+        <v>-0.5897</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1214</v>
+        <v>1.6068</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2571</v>
+        <v>-1.4384</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3123</v>
+        <v>-0.4937</v>
       </c>
       <c r="O7" t="n">
         <v>-0.9447</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2622</v>
+        <v>-1.6556</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4015</v>
+        <v>-0.8067</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8607</v>
+        <v>-0.8489</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.16</v>
+        <v>0.3321</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7145</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8763</v>
+        <v>-2.2418</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3624</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5139</v>
+        <v>-1.3037</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0327</v>
@@ -1078,13 +1078,13 @@
         <v>2.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3012</v>
+        <v>-0.6666</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0151</v>
+        <v>-0.5907</v>
       </c>
       <c r="U8" t="n">
-        <v>0.714</v>
+        <v>-0.0759</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4959</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2061</v>
+        <v>-2.3141</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9047</v>
+        <v>-0.5774</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3014</v>
+        <v>-1.7366</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4214</v>
+        <v>-1.9957</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0834</v>
+        <v>-1.3615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6621</v>
+        <v>-0.6342</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0171</v>
+        <v>0.3909</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5897</v>
+        <v>0.3505</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6068</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4384</v>
+        <v>-2.3866</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4937</v>
+        <v>-1.712</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9447</v>
+        <v>-0.6747</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1168</v>
+        <v>0.3728</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9684</v>
+        <v>0.0083</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1485</v>
+        <v>0.3645</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>-0.8865</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8826</v>
+        <v>-2.4176</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6963</v>
+        <v>-1.2313</v>
       </c>
       <c r="F10" t="n">
         <v>-1.1863</v>
@@ -1234,10 +1234,10 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.121</v>
+        <v>0.3439</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4566</v>
+        <v>0.0083</v>
       </c>
       <c r="U10" t="n">
         <v>0.3356</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5373</v>
+        <v>-3.2473</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1944</v>
+        <v>-2.9316</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3429</v>
+        <v>-0.3157</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5574</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4841</v>
+        <v>-1.1941</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8941</v>
+        <v>-0.6313</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.59</v>
+        <v>-0.5628</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.603499999999999</v>
+        <v>-6.998399999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>1.556600000000001</v>
+        <v>2.1619</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.159899999999999</v>
+        <v>-9.159799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-11.0922</v>
@@ -1390,13 +1390,13 @@
         <v>20.511</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.4887</v>
+        <v>-4.8836</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.056999999999999</v>
+        <v>-3.4519</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4317</v>
+        <v>-1.4318</v>
       </c>
       <c r="V12" t="n">
         <v>1.1639</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2493</v>
+        <v>5.115</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3891</v>
+        <v>4.1757</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8603</v>
+        <v>0.9393</v>
       </c>
       <c r="G13" t="n">
         <v>4.7958</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1565</v>
+        <v>1.0221</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3236</v>
+        <v>0.1102</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8329</v>
+        <v>0.9119</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4843</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4575</v>
+        <v>4.246</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7765</v>
+        <v>2.6754</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6809</v>
+        <v>1.5706</v>
       </c>
       <c r="G14" t="n">
         <v>0.9566</v>
@@ -1546,13 +1546,13 @@
         <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1256</v>
+        <v>1.9142</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7843</v>
+        <v>0.6832</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3413</v>
+        <v>1.231</v>
       </c>
       <c r="V14" t="n">
         <v>0.3985</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8791</v>
+        <v>3.6247</v>
       </c>
       <c r="E15" t="n">
-        <v>3.295</v>
+        <v>3.4972</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4159</v>
+        <v>0.1274</v>
       </c>
       <c r="G15" t="n">
         <v>3.6963</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4485</v>
+        <v>1.1941</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1569</v>
+        <v>0.3592</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2916</v>
+        <v>0.8349</v>
       </c>
       <c r="V15" t="n">
         <v>-0.875</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5335</v>
+        <v>2.4306</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4545</v>
+        <v>1.1623</v>
       </c>
       <c r="F16" t="n">
-        <v>1.079</v>
+        <v>1.2683</v>
       </c>
       <c r="G16" t="n">
         <v>3.6071</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2041</v>
+        <v>1.1012</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5639</v>
+        <v>0.1439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.768</v>
+        <v>0.9573</v>
       </c>
       <c r="V16" t="n">
         <v>0.0664</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5079</v>
+        <v>2.4166</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3691</v>
+        <v>0.541</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8769</v>
+        <v>1.8756</v>
       </c>
       <c r="G17" t="n">
         <v>1.92</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6822</v>
+        <v>1.5909</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5639</v>
+        <v>0.3461</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2461</v>
+        <v>1.2448</v>
       </c>
       <c r="V17" t="n">
         <v>2.2264</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1458</v>
+        <v>0.0435</v>
       </c>
       <c r="E18" t="n">
         <v>2.2348</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3806</v>
+        <v>-2.1913</v>
       </c>
       <c r="G18" t="n">
         <v>1.3743</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6102</v>
+        <v>-0.4209</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3076</v>
+        <v>-0.1183</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2652</v>
+        <v>-0.142</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0605</v>
+        <v>-0.2826</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2047</v>
+        <v>0.1406</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2047</v>
+        <v>0.193</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2047</v>
+        <v>-0.2251</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.4181</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.0166</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3287</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6879</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2047</v>
+        <v>-0.8237</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2047</v>
+        <v>-0.5538</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.2698</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0605</v>
+        <v>-0.335</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0605</v>
+        <v>-0.3225</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0124</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>J. SERRA SÀNCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3507</v>
+        <v>-0.2652</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3837</v>
+        <v>-0.0605</v>
       </c>
       <c r="F20" t="n">
-        <v>0.033</v>
+        <v>-0.2047</v>
       </c>
       <c r="G20" t="n">
-        <v>0.193</v>
+        <v>-0.2047</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2251</v>
+        <v>-0.2047</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4181</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0166</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3287</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8237</v>
+        <v>-0.2047</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5538</v>
+        <v>-0.2047</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5437</v>
+        <v>-0.0605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4237</v>
+        <v>-0.0605</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2026</v>
+        <v>-2.5466</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.045</v>
+        <v>-1.7417</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1576</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1524</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6829</v>
+        <v>-0.0268</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3494</v>
+        <v>-0.046</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3335</v>
+        <v>0.0192</v>
       </c>
       <c r="V22" t="n">
         <v>1.2186</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2783</v>
+        <v>-4.1897</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4203</v>
+        <v>-1.3303</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8581</v>
+        <v>-2.8594</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3499</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8297</v>
+        <v>0.9183</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4914</v>
+        <v>0.5813</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3383</v>
+        <v>0.3369</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.603499999999999</v>
+        <v>8.951700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>9.16</v>
+        <v>9.160000000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5566</v>
+        <v>-0.2082999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>11.0922</v>
@@ -2326,13 +2326,13 @@
         <v>12.6971</v>
       </c>
       <c r="S24" t="n">
-        <v>5.488799999999999</v>
+        <v>6.8371</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4317</v>
+        <v>1.4318</v>
       </c>
       <c r="U24" t="n">
-        <v>4.0571</v>
+        <v>5.4053</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1639</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484238_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484238_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,48 +631,53 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8303</v>
+        <v>1.6094</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9575</v>
+        <v>1.7365</v>
       </c>
       <c r="F3" t="n">
         <v>-0.1271</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4472</v>
+        <v>-0.7738</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0108</v>
+        <v>-0.6247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.458</v>
+        <v>-0.149</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6954</v>
+        <v>0.4744</v>
       </c>
       <c r="K3" t="n">
-        <v>0.967</v>
+        <v>0.353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7284</v>
+        <v>0.1214</v>
       </c>
       <c r="M3" t="n">
         <v>-1.2482</v>
@@ -704,45 +714,50 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8027</v>
+        <v>1.4957</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2389</v>
+        <v>1.9319</v>
       </c>
       <c r="F4" t="n">
         <v>-0.4361</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5089</v>
+        <v>-0.8159</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1865</v>
+        <v>2.8795</v>
       </c>
       <c r="I4" t="n">
         <v>-3.6954</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6826</v>
+        <v>2.3756</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9499</v>
+        <v>3.6429</v>
       </c>
       <c r="L4" t="n">
         <v>-1.2673</v>
@@ -782,681 +797,726 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0179</v>
+        <v>1.221</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8037</v>
+        <v>1.221</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2142</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6398</v>
+        <v>1.221</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0614</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5784</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4728</v>
+        <v>1.221</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4323</v>
+        <v>0.614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1125</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4937</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4581</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1225</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3356</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7411</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6155</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3566</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4251</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2484</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8233</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6822</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5608</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2571</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3123</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9447</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1782</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6444</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5339</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7449</v>
+        <v>-1.0179</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7431</v>
+        <v>-0.8037</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0018</v>
+        <v>-0.2142</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4214</v>
+        <v>-1.6398</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0834</v>
+        <v>-0.0614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6621</v>
+        <v>-1.5784</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0171</v>
+        <v>0.4728</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5897</v>
+        <v>0.4323</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6068</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4384</v>
+        <v>-2.1125</v>
       </c>
       <c r="N7" t="n">
         <v>-0.4937</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9447</v>
+        <v>-1.6188</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6556</v>
+        <v>0.4581</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8067</v>
+        <v>0.1225</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8489</v>
+        <v>0.3356</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2418</v>
+        <v>-1.7411</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9379999999999999</v>
+        <v>1.6155</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3037</v>
+        <v>-3.3566</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0327</v>
+        <v>0.4251</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0312</v>
+        <v>1.2484</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0639</v>
+        <v>-0.8233</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6294</v>
+        <v>2.6822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5346</v>
+        <v>2.5608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6621</v>
+        <v>-2.2571</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5034</v>
+        <v>-1.3123</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1587</v>
+        <v>-0.9447</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9301</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6666</v>
+        <v>-1.1782</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5907</v>
+        <v>-0.6444</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0759</v>
+        <v>-0.5339</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>-2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3141</v>
+        <v>-1.7449</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5774</v>
+        <v>-1.7431</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7366</v>
+        <v>-0.0018</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9957</v>
+        <v>-0.4214</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3615</v>
+        <v>-1.0834</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6342</v>
+        <v>0.6621</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3909</v>
+        <v>1.0171</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3505</v>
+        <v>-0.5897</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>1.6068</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3866</v>
+        <v>-1.4384</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.712</v>
+        <v>-0.4937</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6747</v>
+        <v>-0.9447</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3728</v>
+        <v>-1.6556</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0083</v>
+        <v>-0.8067</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3645</v>
+        <v>-0.8489</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8865</v>
+        <v>0.3321</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4176</v>
+        <v>-2.2418</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2313</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1863</v>
+        <v>-1.3037</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9569</v>
+        <v>-2.0327</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5388</v>
+        <v>0.0312</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4181</v>
+        <v>-2.0639</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7138</v>
+        <v>0.6294</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1615</v>
+        <v>0.5346</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8752</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6707</v>
+        <v>-2.6621</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3773</v>
+        <v>-0.5034</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2933</v>
+        <v>-2.1587</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>2.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3439</v>
+        <v>-0.6666</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0083</v>
+        <v>-0.5907</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3356</v>
+        <v>-0.0759</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2473</v>
+        <v>-2.3141</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9316</v>
+        <v>-0.5774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3157</v>
+        <v>-1.7366</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5574</v>
+        <v>-1.9957</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1543</v>
+        <v>-1.3615</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4031</v>
+        <v>-0.6342</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3236</v>
+        <v>0.3909</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7304</v>
+        <v>0.3505</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2338</v>
+        <v>-2.3866</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4239</v>
+        <v>-1.712</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8099</v>
+        <v>-0.6747</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1941</v>
+        <v>0.3728</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6313</v>
+        <v>0.0083</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5628</v>
+        <v>0.3645</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.998399999999998</v>
+        <v>-2.4176</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1619</v>
+        <v>-1.2313</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.159799999999999</v>
+        <v>-1.1863</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.0922</v>
+        <v>-2.9569</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3007</v>
+        <v>-2.5388</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.7914</v>
+        <v>-0.4181</v>
       </c>
       <c r="J12" t="n">
-        <v>12.1052</v>
+        <v>0.7138</v>
       </c>
       <c r="K12" t="n">
-        <v>8.729699999999999</v>
+        <v>-1.1615</v>
       </c>
       <c r="L12" t="n">
-        <v>3.3754</v>
+        <v>1.8752</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.1973</v>
+        <v>-3.6707</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.0303</v>
+        <v>-1.3773</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.1668</v>
+        <v>-2.2933</v>
       </c>
       <c r="P12" t="n">
-        <v>7.813699999999999</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6971</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>20.511</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.8836</v>
+        <v>0.3439</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4519</v>
+        <v>0.0083</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4318</v>
+        <v>0.3356</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1639</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>6.205900000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.042</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.115</v>
+        <v>-3.2473</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1757</v>
+        <v>-2.9316</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9393</v>
+        <v>-0.3157</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7958</v>
+        <v>-2.5574</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6805</v>
+        <v>-1.1543</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1153</v>
+        <v>-1.4031</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3743</v>
+        <v>-1.3236</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6631</v>
+        <v>-0.7304</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7112</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5785</v>
+        <v>-1.2338</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9826</v>
+        <v>-0.4239</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4041</v>
+        <v>-0.8099</v>
       </c>
       <c r="P13" t="n">
         <v>0.7814</v>
@@ -1468,106 +1528,112 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0221</v>
+        <v>-1.1941</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1102</v>
+        <v>-0.6313</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9119</v>
+        <v>-0.5628</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4843</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1522</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.246</v>
+        <v>-6.998299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6754</v>
+        <v>2.161900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5706</v>
+        <v>-9.159799999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9566</v>
+        <v>-11.0922</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6884</v>
+        <v>-0.3006000000000006</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6451</v>
+        <v>-10.7914</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8052</v>
+        <v>12.1052</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.38</v>
+        <v>8.729699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1851</v>
+        <v>3.3754</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8485</v>
+        <v>-23.1973</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3085</v>
+        <v>-9.0303</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5401</v>
+        <v>-14.1668</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>7.813699999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-12.6971</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>20.511</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9142</v>
+        <v>-4.8836</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6832</v>
+        <v>-3.451899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.231</v>
+        <v>-1.4318</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3985</v>
+        <v>1.163899999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1638</v>
+        <v>6.2059</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7653</v>
-      </c>
+        <v>-5.042</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6247</v>
+        <v>5.115</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4972</v>
+        <v>4.1757</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1274</v>
+        <v>0.9393</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6963</v>
+        <v>4.7958</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3382</v>
+        <v>1.6805</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3581</v>
+        <v>3.1153</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8143</v>
+        <v>5.3743</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4556</v>
+        <v>2.6631</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3587</v>
+        <v>2.7112</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.118</v>
+        <v>-0.5785</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1174</v>
+        <v>-0.9826</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4041</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1941</v>
+        <v>1.0221</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3592</v>
+        <v>0.1102</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8349</v>
+        <v>0.9119</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.875</v>
+        <v>-1.4843</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
         <v>-1.1522</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4306</v>
+        <v>3.6391</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1623</v>
+        <v>2.0684</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2683</v>
+        <v>1.5706</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6071</v>
+        <v>0.3497</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4083</v>
+        <v>-0.6884</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1988</v>
+        <v>1.0381</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9253</v>
+        <v>1.1982</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7818</v>
+        <v>-0.38</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1435</v>
+        <v>1.5782</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3182</v>
+        <v>-0.8485</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3735</v>
+        <v>-0.3085</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9447</v>
+        <v>-0.5401</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3441</v>
+        <v>0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1012</v>
+        <v>1.9142</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1439</v>
+        <v>0.6832</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9573</v>
+        <v>1.231</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0664</v>
+        <v>0.3985</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0664</v>
+        <v>-0.7653</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4166</v>
+        <v>3.6247</v>
       </c>
       <c r="E17" t="n">
-        <v>0.541</v>
+        <v>3.4972</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8756</v>
+        <v>0.1274</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>3.6963</v>
       </c>
       <c r="H17" t="n">
-        <v>2.647</v>
+        <v>0.3382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.727</v>
+        <v>3.3581</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3639</v>
+        <v>4.8143</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0903</v>
+        <v>1.4556</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7264</v>
+        <v>3.3587</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4439</v>
+        <v>-1.118</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4433</v>
+        <v>-1.1174</v>
       </c>
       <c r="O17" t="n">
         <v>-0.0005999999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3208</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5909</v>
+        <v>1.1941</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3461</v>
+        <v>0.3592</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2448</v>
+        <v>0.8349</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2264</v>
+        <v>-0.875</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.488</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0435</v>
+        <v>2.4306</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2348</v>
+        <v>1.1623</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1913</v>
+        <v>1.2683</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3743</v>
+        <v>3.6071</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4856</v>
+        <v>1.4083</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8598</v>
+        <v>2.1988</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5374</v>
+        <v>4.9253</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5921999999999999</v>
+        <v>1.7818</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1297</v>
+        <v>3.1435</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1632</v>
+        <v>-1.3182</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8933</v>
+        <v>-0.3735</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4209</v>
+        <v>1.1012</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3026</v>
+        <v>0.1439</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1183</v>
+        <v>0.9573</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>0.0664</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.142</v>
+        <v>2.4166</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2826</v>
+        <v>0.541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1406</v>
+        <v>1.8756</v>
       </c>
       <c r="G19" t="n">
-        <v>0.193</v>
+        <v>1.92</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2251</v>
+        <v>2.647</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4181</v>
+        <v>-0.727</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0166</v>
+        <v>2.3639</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3287</v>
+        <v>3.0903</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>-0.7264</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8237</v>
+        <v>-0.4439</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5538</v>
+        <v>-0.4433</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2698</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.335</v>
+        <v>1.5909</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3225</v>
+        <v>0.3461</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0124</v>
+        <v>1.2448</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.2264</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.488</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,37 +2060,37 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2652</v>
+        <v>0.607</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0605</v>
+        <v>0.607</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2047</v>
+        <v>0.607</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2014,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7812</v>
+        <v>0.0435</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7113</v>
+        <v>2.2348</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0698</v>
+        <v>-2.1913</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7439</v>
+        <v>1.3743</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8788</v>
+        <v>-1.4856</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1348</v>
+        <v>2.8598</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6741</v>
+        <v>2.5374</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6741</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.1297</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0698</v>
+        <v>-1.1632</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2047</v>
+        <v>-0.8933</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>-0.2698</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0605</v>
+        <v>-0.4209</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0605</v>
+        <v>-0.3026</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.1183</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5466</v>
+        <v>-0.142</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7417</v>
+        <v>-0.2826</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.1406</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1524</v>
+        <v>0.193</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.2251</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3192</v>
+        <v>0.4181</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9609</v>
+        <v>1.0166</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8186</v>
+        <v>0.3287</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7795</v>
+        <v>0.6879</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1915</v>
+        <v>-0.8237</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6518</v>
+        <v>-0.5538</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5397</v>
+        <v>-0.2698</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0268</v>
+        <v>-0.335</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.046</v>
+        <v>-0.3225</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0192</v>
+        <v>-0.0124</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1897</v>
+        <v>-0.2652</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3303</v>
+        <v>-0.0605</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8594</v>
+        <v>-0.2047</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3499</v>
+        <v>-0.2047</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4577</v>
+        <v>-0.2047</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1078</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9952</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5385</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3451</v>
+        <v>-0.2047</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9962</v>
+        <v>-0.2047</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.349</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9183</v>
+        <v>-0.0605</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5813</v>
+        <v>-0.0605</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.951700000000001</v>
+        <v>-1.7812</v>
       </c>
       <c r="E24" t="n">
-        <v>9.160000000000002</v>
+        <v>-1.7113</v>
       </c>
       <c r="F24" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.7439</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.8788</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2047</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.0605</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0605</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. AURO GARRIGA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.5466</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.7417</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.8048999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.1524</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.8332000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.3192</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.9609</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8186</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.7795</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.1915</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.6518</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5397</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. SOTO CAPARROS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.1897</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.3303</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.8594</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.3499</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4577</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.9952</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-3.3451</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.9962</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.349</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.5395</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484238_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.9518</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="F27" t="n">
         <v>-0.2082999999999999</v>
       </c>
-      <c r="G24" t="n">
-        <v>11.0922</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G27" t="n">
+        <v>11.0923</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.3005</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>10.7916</v>
       </c>
-      <c r="J24" t="n">
-        <v>23.1972</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J27" t="n">
+        <v>23.19720000000001</v>
+      </c>
+      <c r="K27" t="n">
         <v>9.0303</v>
       </c>
-      <c r="L24" t="n">
-        <v>14.167</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L27" t="n">
+        <v>14.1671</v>
+      </c>
+      <c r="M27" t="n">
         <v>-12.1051</v>
       </c>
-      <c r="N24" t="n">
-        <v>-8.729800000000001</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N27" t="n">
+        <v>-8.729799999999999</v>
+      </c>
+      <c r="O27" t="n">
         <v>-3.3754</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-7.813700000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-20.511</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>12.6971</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>6.8371</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>1.4318</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>5.4053</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-1.1639</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>5.042</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-6.2058</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
